--- a/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95210826-F7B2-4926-888F-9B0A721C6B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5992E8FA-F42F-4536-A9D2-FEBFE5AA6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="寒冷爆发力" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$F$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="1994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1996">
   <si>
     <t>undefined</t>
   </si>
@@ -6686,6 +6686,14 @@
   </si>
   <si>
     <t>车臣乌拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扎布汗省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂特冈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -31858,7 +31866,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="30" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="24" customWidth="1"/>
@@ -32802,37 +32810,37 @@
     </row>
     <row r="53" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="95">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B53" s="109" t="s">
-        <v>1789</v>
+        <v>1994</v>
       </c>
       <c r="C53" s="96" t="s">
-        <v>1791</v>
+        <v>1995</v>
       </c>
       <c r="D53" s="97">
-        <v>-45.4</v>
+        <v>-51.9</v>
       </c>
       <c r="E53" s="98">
-        <v>42763</v>
+        <v>42423</v>
       </c>
       <c r="F53" s="103"/>
     </row>
     <row r="54" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="95">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B54" s="109" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C54" s="96" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="D54" s="97">
-        <v>-51.6</v>
+        <v>-45.4</v>
       </c>
       <c r="E54" s="98">
-        <v>43123</v>
+        <v>42763</v>
       </c>
       <c r="F54" s="103"/>
     </row>
@@ -32841,13 +32849,13 @@
         <v>2018</v>
       </c>
       <c r="B55" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C55" s="96" t="s">
-        <v>1867</v>
+        <v>1790</v>
       </c>
       <c r="D55" s="97">
-        <v>-51.3</v>
+        <v>-51.6</v>
       </c>
       <c r="E55" s="98">
         <v>43123</v>
@@ -32859,16 +32867,16 @@
         <v>2018</v>
       </c>
       <c r="B56" s="109" t="s">
-        <v>1788</v>
+        <v>1970</v>
       </c>
       <c r="C56" s="96" t="s">
-        <v>1790</v>
+        <v>1867</v>
       </c>
       <c r="D56" s="97">
-        <v>-53.2</v>
+        <v>-51.3</v>
       </c>
       <c r="E56" s="98">
-        <v>43124</v>
+        <v>43123</v>
       </c>
       <c r="F56" s="103"/>
     </row>
@@ -32877,13 +32885,13 @@
         <v>2018</v>
       </c>
       <c r="B57" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C57" s="96" t="s">
-        <v>1867</v>
+        <v>1790</v>
       </c>
       <c r="D57" s="97">
-        <v>-51.7</v>
+        <v>-53.2</v>
       </c>
       <c r="E57" s="98">
         <v>43124</v>
@@ -32901,10 +32909,10 @@
         <v>1867</v>
       </c>
       <c r="D58" s="97">
-        <v>-50.7</v>
+        <v>-51.7</v>
       </c>
       <c r="E58" s="98">
-        <v>43125</v>
+        <v>43124</v>
       </c>
       <c r="F58" s="103"/>
     </row>
@@ -32916,10 +32924,10 @@
         <v>1970</v>
       </c>
       <c r="C59" s="96" t="s">
-        <v>1979</v>
+        <v>1867</v>
       </c>
       <c r="D59" s="97">
-        <v>-50.3</v>
+        <v>-50.7</v>
       </c>
       <c r="E59" s="98">
         <v>43125</v>
@@ -32931,13 +32939,13 @@
         <v>2018</v>
       </c>
       <c r="B60" s="109" t="s">
-        <v>1788</v>
+        <v>1970</v>
       </c>
       <c r="C60" s="96" t="s">
-        <v>1790</v>
+        <v>1979</v>
       </c>
       <c r="D60" s="97">
-        <v>-50.1</v>
+        <v>-50.3</v>
       </c>
       <c r="E60" s="98">
         <v>43125</v>
@@ -32949,54 +32957,54 @@
         <v>2018</v>
       </c>
       <c r="B61" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C61" s="96" t="s">
-        <v>1867</v>
+        <v>1790</v>
       </c>
       <c r="D61" s="97">
-        <v>-50.2</v>
+        <v>-50.1</v>
       </c>
       <c r="E61" s="98">
-        <v>43126</v>
-      </c>
-      <c r="F61" s="103" t="s">
-        <v>1978</v>
-      </c>
+        <v>43125</v>
+      </c>
+      <c r="F61" s="103"/>
     </row>
     <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="95">
         <v>2018</v>
       </c>
       <c r="B62" s="109" t="s">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>1794</v>
+        <v>1867</v>
       </c>
       <c r="D62" s="97">
-        <v>-49.9</v>
+        <v>-50.2</v>
       </c>
       <c r="E62" s="98">
         <v>43126</v>
       </c>
-      <c r="F62" s="103"/>
+      <c r="F62" s="103" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="95">
         <v>2018</v>
       </c>
       <c r="B63" s="109" t="s">
-        <v>1788</v>
+        <v>1947</v>
       </c>
       <c r="C63" s="96" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="D63" s="97">
-        <v>-51.8</v>
+        <v>-49.9</v>
       </c>
       <c r="E63" s="98">
-        <v>43127</v>
+        <v>43126</v>
       </c>
       <c r="F63" s="103"/>
     </row>
@@ -33005,20 +33013,18 @@
         <v>2018</v>
       </c>
       <c r="B64" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="D64" s="97">
-        <v>-50</v>
-      </c>
-      <c r="E64" s="98" t="s">
-        <v>1973</v>
-      </c>
-      <c r="F64" s="103" t="s">
-        <v>1983</v>
-      </c>
+        <v>-51.8</v>
+      </c>
+      <c r="E64" s="98">
+        <v>43127</v>
+      </c>
+      <c r="F64" s="103"/>
     </row>
     <row r="65" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="95">
@@ -33028,7 +33034,7 @@
         <v>1970</v>
       </c>
       <c r="C65" s="96" t="s">
-        <v>1971</v>
+        <v>1794</v>
       </c>
       <c r="D65" s="97">
         <v>-50</v>
@@ -33048,7 +33054,7 @@
         <v>1970</v>
       </c>
       <c r="C66" s="96" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D66" s="97">
         <v>-50</v>
@@ -33065,60 +33071,62 @@
         <v>2018</v>
       </c>
       <c r="B67" s="109" t="s">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="C67" s="96" t="s">
-        <v>1794</v>
+        <v>1972</v>
       </c>
       <c r="D67" s="97">
         <v>-50</v>
       </c>
       <c r="E67" s="98" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="F67" s="103" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="95">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B68" s="109" t="s">
-        <v>1788</v>
+        <v>1947</v>
       </c>
       <c r="C68" s="96" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="D68" s="97">
-        <v>-48.4</v>
-      </c>
-      <c r="E68" s="98">
-        <v>43828</v>
-      </c>
-      <c r="F68" s="103"/>
+        <v>-50</v>
+      </c>
+      <c r="E68" s="98" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F68" s="103" t="s">
+        <v>1977</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="95">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B69" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C69" s="96" t="s">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="D69" s="97">
-        <v>-49.6</v>
+        <v>-48.4</v>
       </c>
       <c r="E69" s="98">
-        <v>44194</v>
+        <v>43828</v>
       </c>
       <c r="F69" s="103"/>
     </row>
     <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="95">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B70" s="109" t="s">
         <v>1788</v>
@@ -33127,67 +33135,65 @@
         <v>1784</v>
       </c>
       <c r="D70" s="97">
-        <v>-47.2</v>
+        <v>-49.6</v>
       </c>
       <c r="E70" s="98">
-        <v>44200</v>
+        <v>44194</v>
       </c>
       <c r="F70" s="103"/>
     </row>
     <row r="71" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="95">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B71" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C71" s="96" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="D71" s="97">
-        <v>-46.8</v>
-      </c>
-      <c r="E71" s="98"/>
+        <v>-47.2</v>
+      </c>
+      <c r="E71" s="98">
+        <v>44200</v>
+      </c>
       <c r="F71" s="103"/>
     </row>
     <row r="72" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="95">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B72" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C72" s="96" t="s">
-        <v>1867</v>
+        <v>1785</v>
       </c>
       <c r="D72" s="97">
-        <v>-50</v>
-      </c>
-      <c r="E72" s="98">
-        <v>44949</v>
-      </c>
-      <c r="F72" s="103" t="s">
-        <v>1982</v>
-      </c>
+        <v>-46.8</v>
+      </c>
+      <c r="E72" s="98"/>
+      <c r="F72" s="103"/>
     </row>
     <row r="73" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="95">
         <v>2023</v>
       </c>
       <c r="B73" s="109" t="s">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="C73" s="96" t="s">
-        <v>1948</v>
+        <v>1867</v>
       </c>
       <c r="D73" s="97">
-        <v>-49.4</v>
+        <v>-50</v>
       </c>
       <c r="E73" s="98">
-        <v>45279</v>
+        <v>44949</v>
       </c>
       <c r="F73" s="103" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -33200,53 +33206,53 @@
       <c r="C74" s="96" t="s">
         <v>1948</v>
       </c>
-      <c r="D74" s="99">
-        <v>-50</v>
+      <c r="D74" s="97">
+        <v>-49.4</v>
       </c>
       <c r="E74" s="98">
-        <v>45280</v>
+        <v>45279</v>
       </c>
       <c r="F74" s="103" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="95">
+        <v>2023</v>
+      </c>
+      <c r="B75" s="109" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C75" s="96" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D75" s="99">
+        <v>-50</v>
+      </c>
+      <c r="E75" s="98">
+        <v>45280</v>
+      </c>
+      <c r="F75" s="103" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="95">
         <v>2024</v>
-      </c>
-      <c r="B75" s="109" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C75" s="96" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D75" s="97">
-        <v>-48.8</v>
-      </c>
-      <c r="E75" s="98">
-        <v>45312</v>
-      </c>
-      <c r="F75" s="103"/>
-    </row>
-    <row r="76" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="100">
-        <v>2025</v>
       </c>
       <c r="B76" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C76" s="96" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="D76" s="97">
-        <v>-45.6</v>
+        <v>-48.8</v>
       </c>
       <c r="E76" s="98">
-        <v>45659</v>
-      </c>
-      <c r="F76" s="103" t="s">
-        <v>1980</v>
-      </c>
+        <v>45312</v>
+      </c>
+      <c r="F76" s="103"/>
     </row>
     <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="100">
@@ -33256,56 +33262,56 @@
         <v>1788</v>
       </c>
       <c r="C77" s="96" t="s">
-        <v>1794</v>
+        <v>1785</v>
       </c>
       <c r="D77" s="97">
         <v>-45.6</v>
       </c>
       <c r="E77" s="98">
-        <v>45673</v>
+        <v>45659</v>
       </c>
       <c r="F77" s="103" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="100">
         <v>2025</v>
       </c>
       <c r="B78" s="109" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C78" s="96" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="D78" s="97">
-        <v>-44.2</v>
+        <v>-45.6</v>
       </c>
       <c r="E78" s="98">
         <v>45673</v>
       </c>
-      <c r="F78" s="106" t="s">
+      <c r="F78" s="103" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="100">
+        <v>2025</v>
+      </c>
+      <c r="B79" s="109" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C79" s="96" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D79" s="97">
+        <v>-44.2</v>
+      </c>
+      <c r="E79" s="98">
+        <v>45673</v>
+      </c>
+      <c r="F79" s="106" t="s">
         <v>1974</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="100">
-        <v>2026</v>
-      </c>
-      <c r="B79" s="109" t="s">
-        <v>1970</v>
-      </c>
-      <c r="C79" s="96" t="s">
-        <v>1794</v>
-      </c>
-      <c r="D79" s="97">
-        <v>-51.2</v>
-      </c>
-      <c r="E79" s="101">
-        <v>46039</v>
-      </c>
-      <c r="F79" s="103" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -33319,10 +33325,10 @@
         <v>1794</v>
       </c>
       <c r="D80" s="97">
-        <v>-52</v>
+        <v>-51.2</v>
       </c>
       <c r="E80" s="101">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="F80" s="103" t="s">
         <v>1980</v>
@@ -33336,10 +33342,10 @@
         <v>1970</v>
       </c>
       <c r="C81" s="96" t="s">
-        <v>1867</v>
+        <v>1794</v>
       </c>
       <c r="D81" s="97">
-        <v>-51.1</v>
+        <v>-52</v>
       </c>
       <c r="E81" s="101">
         <v>46040</v>
@@ -33348,17 +33354,37 @@
         <v>1980</v>
       </c>
     </row>
+    <row r="82" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="100">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="109" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C82" s="96" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D82" s="97">
+        <v>-51.1</v>
+      </c>
+      <c r="E82" s="101">
+        <v>46040</v>
+      </c>
+      <c r="F82" s="103" t="s">
+        <v>1980</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F81" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F81">
-      <sortCondition ref="A2:A81"/>
+  <autoFilter ref="A2:F82" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F82">
+      <sortCondition ref="A2:A82"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D3:D81">
+  <conditionalFormatting sqref="D3:D82">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>

--- a/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5992E8FA-F42F-4536-A9D2-FEBFE5AA6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B9E3E4-E97D-4118-BD67-75385002A716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="寒冷爆发力" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$F$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$F$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="2000">
   <si>
     <t>undefined</t>
   </si>
@@ -6694,6 +6694,22 @@
   </si>
   <si>
     <t>鄂特冈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扎布汗省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂特冈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扎布汗省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>车臣乌拉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -31866,7 +31882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="30" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="24" customWidth="1"/>
@@ -32741,16 +32757,16 @@
         <v>2016</v>
       </c>
       <c r="B49" s="109" t="s">
-        <v>1788</v>
+        <v>1996</v>
       </c>
       <c r="C49" s="96" t="s">
-        <v>1790</v>
+        <v>1997</v>
       </c>
       <c r="D49" s="97">
-        <v>-50.3</v>
+        <v>-50</v>
       </c>
       <c r="E49" s="98">
-        <v>42437</v>
+        <v>42436</v>
       </c>
       <c r="F49" s="103"/>
     </row>
@@ -32759,16 +32775,16 @@
         <v>2016</v>
       </c>
       <c r="B50" s="109" t="s">
-        <v>1788</v>
+        <v>1998</v>
       </c>
       <c r="C50" s="96" t="s">
-        <v>1790</v>
+        <v>1999</v>
       </c>
       <c r="D50" s="97">
-        <v>-54</v>
+        <v>-47.4</v>
       </c>
       <c r="E50" s="98">
-        <v>42438</v>
+        <v>42436</v>
       </c>
       <c r="F50" s="103"/>
     </row>
@@ -32783,10 +32799,10 @@
         <v>1790</v>
       </c>
       <c r="D51" s="97">
-        <v>-53</v>
+        <v>-50.3</v>
       </c>
       <c r="E51" s="98">
-        <v>42439</v>
+        <v>42437</v>
       </c>
       <c r="F51" s="103"/>
     </row>
@@ -32795,16 +32811,16 @@
         <v>2016</v>
       </c>
       <c r="B52" s="109" t="s">
-        <v>1992</v>
+        <v>1788</v>
       </c>
       <c r="C52" s="96" t="s">
-        <v>1993</v>
+        <v>1790</v>
       </c>
       <c r="D52" s="97">
-        <v>-50.2</v>
+        <v>-54</v>
       </c>
       <c r="E52" s="98">
-        <v>42422</v>
+        <v>42438</v>
       </c>
       <c r="F52" s="103"/>
     </row>
@@ -32813,70 +32829,70 @@
         <v>2016</v>
       </c>
       <c r="B53" s="109" t="s">
-        <v>1994</v>
+        <v>1788</v>
       </c>
       <c r="C53" s="96" t="s">
-        <v>1995</v>
+        <v>1790</v>
       </c>
       <c r="D53" s="97">
-        <v>-51.9</v>
+        <v>-53</v>
       </c>
       <c r="E53" s="98">
-        <v>42423</v>
+        <v>42439</v>
       </c>
       <c r="F53" s="103"/>
     </row>
     <row r="54" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="95">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B54" s="109" t="s">
-        <v>1789</v>
+        <v>1992</v>
       </c>
       <c r="C54" s="96" t="s">
-        <v>1791</v>
+        <v>1993</v>
       </c>
       <c r="D54" s="97">
-        <v>-45.4</v>
+        <v>-50.2</v>
       </c>
       <c r="E54" s="98">
-        <v>42763</v>
+        <v>42422</v>
       </c>
       <c r="F54" s="103"/>
     </row>
     <row r="55" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="95">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B55" s="109" t="s">
-        <v>1788</v>
+        <v>1994</v>
       </c>
       <c r="C55" s="96" t="s">
-        <v>1790</v>
+        <v>1995</v>
       </c>
       <c r="D55" s="97">
-        <v>-51.6</v>
+        <v>-51.9</v>
       </c>
       <c r="E55" s="98">
-        <v>43123</v>
+        <v>42423</v>
       </c>
       <c r="F55" s="103"/>
     </row>
     <row r="56" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="95">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B56" s="109" t="s">
-        <v>1970</v>
+        <v>1789</v>
       </c>
       <c r="C56" s="96" t="s">
-        <v>1867</v>
+        <v>1791</v>
       </c>
       <c r="D56" s="97">
-        <v>-51.3</v>
+        <v>-45.4</v>
       </c>
       <c r="E56" s="98">
-        <v>43123</v>
+        <v>42763</v>
       </c>
       <c r="F56" s="103"/>
     </row>
@@ -32891,10 +32907,10 @@
         <v>1790</v>
       </c>
       <c r="D57" s="97">
-        <v>-53.2</v>
+        <v>-51.6</v>
       </c>
       <c r="E57" s="98">
-        <v>43124</v>
+        <v>43123</v>
       </c>
       <c r="F57" s="103"/>
     </row>
@@ -32909,10 +32925,10 @@
         <v>1867</v>
       </c>
       <c r="D58" s="97">
-        <v>-51.7</v>
+        <v>-51.3</v>
       </c>
       <c r="E58" s="98">
-        <v>43124</v>
+        <v>43123</v>
       </c>
       <c r="F58" s="103"/>
     </row>
@@ -32921,16 +32937,16 @@
         <v>2018</v>
       </c>
       <c r="B59" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C59" s="96" t="s">
-        <v>1867</v>
+        <v>1790</v>
       </c>
       <c r="D59" s="97">
-        <v>-50.7</v>
+        <v>-53.2</v>
       </c>
       <c r="E59" s="98">
-        <v>43125</v>
+        <v>43124</v>
       </c>
       <c r="F59" s="103"/>
     </row>
@@ -32942,13 +32958,13 @@
         <v>1970</v>
       </c>
       <c r="C60" s="96" t="s">
-        <v>1979</v>
+        <v>1867</v>
       </c>
       <c r="D60" s="97">
-        <v>-50.3</v>
+        <v>-51.7</v>
       </c>
       <c r="E60" s="98">
-        <v>43125</v>
+        <v>43124</v>
       </c>
       <c r="F60" s="103"/>
     </row>
@@ -32957,13 +32973,13 @@
         <v>2018</v>
       </c>
       <c r="B61" s="109" t="s">
-        <v>1788</v>
+        <v>1970</v>
       </c>
       <c r="C61" s="96" t="s">
-        <v>1790</v>
+        <v>1867</v>
       </c>
       <c r="D61" s="97">
-        <v>-50.1</v>
+        <v>-50.7</v>
       </c>
       <c r="E61" s="98">
         <v>43125</v>
@@ -32978,33 +32994,31 @@
         <v>1970</v>
       </c>
       <c r="C62" s="96" t="s">
-        <v>1867</v>
+        <v>1979</v>
       </c>
       <c r="D62" s="97">
-        <v>-50.2</v>
+        <v>-50.3</v>
       </c>
       <c r="E62" s="98">
-        <v>43126</v>
-      </c>
-      <c r="F62" s="103" t="s">
-        <v>1978</v>
-      </c>
+        <v>43125</v>
+      </c>
+      <c r="F62" s="103"/>
     </row>
     <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="95">
         <v>2018</v>
       </c>
       <c r="B63" s="109" t="s">
-        <v>1947</v>
+        <v>1788</v>
       </c>
       <c r="C63" s="96" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="D63" s="97">
-        <v>-49.9</v>
+        <v>-50.1</v>
       </c>
       <c r="E63" s="98">
-        <v>43126</v>
+        <v>43125</v>
       </c>
       <c r="F63" s="103"/>
     </row>
@@ -33013,58 +33027,56 @@
         <v>2018</v>
       </c>
       <c r="B64" s="109" t="s">
-        <v>1788</v>
+        <v>1970</v>
       </c>
       <c r="C64" s="96" t="s">
-        <v>1792</v>
+        <v>1867</v>
       </c>
       <c r="D64" s="97">
-        <v>-51.8</v>
+        <v>-50.2</v>
       </c>
       <c r="E64" s="98">
-        <v>43127</v>
-      </c>
-      <c r="F64" s="103"/>
+        <v>43126</v>
+      </c>
+      <c r="F64" s="103" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="95">
         <v>2018</v>
       </c>
       <c r="B65" s="109" t="s">
-        <v>1970</v>
+        <v>1947</v>
       </c>
       <c r="C65" s="96" t="s">
         <v>1794</v>
       </c>
       <c r="D65" s="97">
-        <v>-50</v>
-      </c>
-      <c r="E65" s="98" t="s">
-        <v>1973</v>
-      </c>
-      <c r="F65" s="103" t="s">
-        <v>1983</v>
-      </c>
+        <v>-49.9</v>
+      </c>
+      <c r="E65" s="98">
+        <v>43126</v>
+      </c>
+      <c r="F65" s="103"/>
     </row>
     <row r="66" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="95">
         <v>2018</v>
       </c>
       <c r="B66" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C66" s="96" t="s">
-        <v>1971</v>
+        <v>1792</v>
       </c>
       <c r="D66" s="97">
-        <v>-50</v>
-      </c>
-      <c r="E66" s="98" t="s">
-        <v>1973</v>
-      </c>
-      <c r="F66" s="103" t="s">
-        <v>1983</v>
-      </c>
+        <v>-51.8</v>
+      </c>
+      <c r="E66" s="98">
+        <v>43127</v>
+      </c>
+      <c r="F66" s="103"/>
     </row>
     <row r="67" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="95">
@@ -33074,7 +33086,7 @@
         <v>1970</v>
       </c>
       <c r="C67" s="96" t="s">
-        <v>1972</v>
+        <v>1794</v>
       </c>
       <c r="D67" s="97">
         <v>-50</v>
@@ -33091,146 +33103,146 @@
         <v>2018</v>
       </c>
       <c r="B68" s="109" t="s">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="C68" s="96" t="s">
-        <v>1794</v>
+        <v>1971</v>
       </c>
       <c r="D68" s="97">
         <v>-50</v>
       </c>
       <c r="E68" s="98" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="F68" s="103" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="95">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B69" s="109" t="s">
-        <v>1788</v>
+        <v>1970</v>
       </c>
       <c r="C69" s="96" t="s">
-        <v>1792</v>
+        <v>1972</v>
       </c>
       <c r="D69" s="97">
-        <v>-48.4</v>
-      </c>
-      <c r="E69" s="98">
-        <v>43828</v>
-      </c>
-      <c r="F69" s="103"/>
+        <v>-50</v>
+      </c>
+      <c r="E69" s="98" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F69" s="103" t="s">
+        <v>1983</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="95">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B70" s="109" t="s">
-        <v>1788</v>
+        <v>1947</v>
       </c>
       <c r="C70" s="96" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="D70" s="97">
-        <v>-49.6</v>
-      </c>
-      <c r="E70" s="98">
-        <v>44194</v>
-      </c>
-      <c r="F70" s="103"/>
+        <v>-50</v>
+      </c>
+      <c r="E70" s="98" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F70" s="103" t="s">
+        <v>1977</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="95">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B71" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C71" s="96" t="s">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="D71" s="97">
-        <v>-47.2</v>
+        <v>-48.4</v>
       </c>
       <c r="E71" s="98">
-        <v>44200</v>
+        <v>43828</v>
       </c>
       <c r="F71" s="103"/>
     </row>
     <row r="72" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="95">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B72" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C72" s="96" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="D72" s="97">
-        <v>-46.8</v>
-      </c>
-      <c r="E72" s="98"/>
+        <v>-49.6</v>
+      </c>
+      <c r="E72" s="98">
+        <v>44194</v>
+      </c>
       <c r="F72" s="103"/>
     </row>
     <row r="73" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="95">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B73" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C73" s="96" t="s">
-        <v>1867</v>
+        <v>1784</v>
       </c>
       <c r="D73" s="97">
-        <v>-50</v>
+        <v>-47.2</v>
       </c>
       <c r="E73" s="98">
-        <v>44949</v>
-      </c>
-      <c r="F73" s="103" t="s">
-        <v>1982</v>
-      </c>
+        <v>44200</v>
+      </c>
+      <c r="F73" s="103"/>
     </row>
     <row r="74" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="95">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B74" s="109" t="s">
-        <v>1947</v>
+        <v>1788</v>
       </c>
       <c r="C74" s="96" t="s">
-        <v>1948</v>
+        <v>1785</v>
       </c>
       <c r="D74" s="97">
-        <v>-49.4</v>
-      </c>
-      <c r="E74" s="98">
-        <v>45279</v>
-      </c>
-      <c r="F74" s="103" t="s">
-        <v>1981</v>
-      </c>
+        <v>-46.8</v>
+      </c>
+      <c r="E74" s="98"/>
+      <c r="F74" s="103"/>
     </row>
     <row r="75" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="95">
         <v>2023</v>
       </c>
       <c r="B75" s="109" t="s">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="C75" s="96" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D75" s="99">
+        <v>1867</v>
+      </c>
+      <c r="D75" s="97">
         <v>-50</v>
       </c>
       <c r="E75" s="98">
-        <v>45280</v>
+        <v>44949</v>
       </c>
       <c r="F75" s="103" t="s">
         <v>1982</v>
@@ -33238,120 +33250,120 @@
     </row>
     <row r="76" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="95">
+        <v>2023</v>
+      </c>
+      <c r="B76" s="109" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C76" s="96" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D76" s="97">
+        <v>-49.4</v>
+      </c>
+      <c r="E76" s="98">
+        <v>45279</v>
+      </c>
+      <c r="F76" s="103" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="95">
+        <v>2023</v>
+      </c>
+      <c r="B77" s="109" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C77" s="96" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D77" s="99">
+        <v>-50</v>
+      </c>
+      <c r="E77" s="98">
+        <v>45280</v>
+      </c>
+      <c r="F77" s="103" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="95">
         <v>2024</v>
-      </c>
-      <c r="B76" s="109" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C76" s="96" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D76" s="97">
-        <v>-48.8</v>
-      </c>
-      <c r="E76" s="98">
-        <v>45312</v>
-      </c>
-      <c r="F76" s="103"/>
-    </row>
-    <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="100">
-        <v>2025</v>
-      </c>
-      <c r="B77" s="109" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C77" s="96" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D77" s="97">
-        <v>-45.6</v>
-      </c>
-      <c r="E77" s="98">
-        <v>45659</v>
-      </c>
-      <c r="F77" s="103" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="100">
-        <v>2025</v>
       </c>
       <c r="B78" s="109" t="s">
         <v>1788</v>
       </c>
       <c r="C78" s="96" t="s">
-        <v>1794</v>
+        <v>1784</v>
       </c>
       <c r="D78" s="97">
-        <v>-45.6</v>
+        <v>-48.8</v>
       </c>
       <c r="E78" s="98">
-        <v>45673</v>
-      </c>
-      <c r="F78" s="103" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>45312</v>
+      </c>
+      <c r="F78" s="103"/>
+    </row>
+    <row r="79" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="100">
         <v>2025</v>
       </c>
       <c r="B79" s="109" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C79" s="96" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="D79" s="97">
-        <v>-44.2</v>
+        <v>-45.6</v>
       </c>
       <c r="E79" s="98">
-        <v>45673</v>
-      </c>
-      <c r="F79" s="106" t="s">
-        <v>1974</v>
+        <v>45659</v>
+      </c>
+      <c r="F79" s="103" t="s">
+        <v>1980</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="100">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B80" s="109" t="s">
-        <v>1970</v>
+        <v>1788</v>
       </c>
       <c r="C80" s="96" t="s">
         <v>1794</v>
       </c>
       <c r="D80" s="97">
-        <v>-51.2</v>
-      </c>
-      <c r="E80" s="101">
-        <v>46039</v>
+        <v>-45.6</v>
+      </c>
+      <c r="E80" s="98">
+        <v>45673</v>
       </c>
       <c r="F80" s="103" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="100">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B81" s="109" t="s">
-        <v>1970</v>
+        <v>1789</v>
       </c>
       <c r="C81" s="96" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D81" s="97">
-        <v>-52</v>
-      </c>
-      <c r="E81" s="101">
-        <v>46040</v>
-      </c>
-      <c r="F81" s="103" t="s">
-        <v>1980</v>
+        <v>-44.2</v>
+      </c>
+      <c r="E81" s="98">
+        <v>45673</v>
+      </c>
+      <c r="F81" s="106" t="s">
+        <v>1974</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -33362,29 +33374,69 @@
         <v>1970</v>
       </c>
       <c r="C82" s="96" t="s">
-        <v>1867</v>
+        <v>1794</v>
       </c>
       <c r="D82" s="97">
-        <v>-51.1</v>
+        <v>-51.2</v>
       </c>
       <c r="E82" s="101">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="F82" s="103" t="s">
         <v>1980</v>
       </c>
     </row>
+    <row r="83" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="100">
+        <v>2026</v>
+      </c>
+      <c r="B83" s="109" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C83" s="96" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D83" s="97">
+        <v>-52</v>
+      </c>
+      <c r="E83" s="101">
+        <v>46040</v>
+      </c>
+      <c r="F83" s="103" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="100">
+        <v>2026</v>
+      </c>
+      <c r="B84" s="109" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C84" s="96" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D84" s="97">
+        <v>-51.1</v>
+      </c>
+      <c r="E84" s="101">
+        <v>46040</v>
+      </c>
+      <c r="F84" s="103" t="s">
+        <v>1980</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F82" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F82">
-      <sortCondition ref="A2:A82"/>
+  <autoFilter ref="A2:F84" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F84">
+      <sortCondition ref="A2:A84"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D3:D82">
+  <conditionalFormatting sqref="D3:D84">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>

--- a/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B9E3E4-E97D-4118-BD67-75385002A716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17DE7C9-8FB3-465F-A5A8-72F79682EC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
@@ -32799,7 +32799,7 @@
         <v>1790</v>
       </c>
       <c r="D51" s="97">
-        <v>-50.3</v>
+        <v>-50.8</v>
       </c>
       <c r="E51" s="98">
         <v>42437</v>

--- a/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古-50记录 & 东亚极端冷月均温排名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17DE7C9-8FB3-465F-A5A8-72F79682EC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF8F52D-56EC-4CD1-9534-C546EEF44E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
@@ -32817,7 +32817,7 @@
         <v>1790</v>
       </c>
       <c r="D52" s="97">
-        <v>-54</v>
+        <v>-54.2</v>
       </c>
       <c r="E52" s="98">
         <v>42438</v>
